--- a/Result/checksun/水泥工業.xlsx
+++ b/Result/checksun/水泥工業.xlsx
@@ -723,7 +723,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>97</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>97</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>97</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>97</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>97</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>97</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>97</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>97</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>97</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>97</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>97</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3945,24 +3945,24 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>-12.0</t>
@@ -3975,12 +3975,12 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>16.61</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>16.61</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>16.61</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>16.61</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>16.61</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>16.61</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>16.61</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>16.61</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>16.61</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>16.61</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>16.61</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -7067,7 +7067,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
@@ -10239,7 +10239,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>強勢股;反彈型股</t>
+          <t>強勢股;【b】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -10289,24 +10289,24 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t>-1.37</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>-6.0</t>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -10479,7 +10479,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -10494,12 +10494,12 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -10607,12 +10607,12 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -10712,7 +10712,7 @@
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -10782,12 +10782,12 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -10895,12 +10895,12 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -11070,12 +11070,12 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -11358,12 +11358,12 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -11441,24 +11441,24 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t>-1.37</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O39" t="inlineStr">
         <is>
           <t>-23.0</t>
@@ -11471,12 +11471,12 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -11646,12 +11646,12 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -11759,12 +11759,12 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
@@ -12305,7 +12305,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -12335,12 +12335,12 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -12440,7 +12440,7 @@
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -12728,7 +12728,7 @@
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -12798,12 +12798,12 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -12911,12 +12911,12 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -13086,12 +13086,12 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
@@ -13169,7 +13169,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -13199,12 +13199,12 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -13374,12 +13374,12 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
@@ -13411,7 +13411,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>111.25</t>
+          <t>109.58</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -13666,12 +13666,12 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
@@ -13749,7 +13749,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -13779,12 +13779,12 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>111.25</t>
+          <t>109.58</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -14067,12 +14067,12 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>111.25</t>
+          <t>109.58</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -14355,12 +14355,12 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>111.25</t>
+          <t>109.58</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
@@ -14530,12 +14530,12 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
@@ -14613,99 +14613,99 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
+          <t>-1.52</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1593</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>-0.37</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>-1.62</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>-3.17</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>13.62</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>14.066</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>1463</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>-0.37</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>-1.62</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>-3.17</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>13.4</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>13.62</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>14.066</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AD50" t="inlineStr">
         <is>
           <t>28.86</t>
@@ -14793,7 +14793,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>111.25</t>
+          <t>109.58</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>111.25</t>
+          <t>109.58</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
@@ -15106,12 +15106,12 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>111.25</t>
+          <t>109.58</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
@@ -15394,12 +15394,12 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -15507,12 +15507,12 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>111.25</t>
+          <t>109.58</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
@@ -15682,12 +15682,12 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -15795,12 +15795,12 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>111.25</t>
+          <t>109.58</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -15970,12 +15970,12 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -16233,7 +16233,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -16243,7 +16243,7 @@
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>111.25</t>
+          <t>109.58</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
@@ -16341,7 +16341,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -16521,7 +16521,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>111.25</t>
+          <t>109.58</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -16546,12 +16546,12 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
@@ -16583,7 +16583,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>多頭排列股</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -16663,12 +16663,12 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
@@ -16951,12 +16951,12 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -17126,7 +17126,7 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
@@ -17239,12 +17239,12 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -17414,7 +17414,7 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
@@ -17527,12 +17527,12 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -17702,7 +17702,7 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
@@ -17815,12 +17815,12 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -17990,7 +17990,7 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
@@ -18103,12 +18103,12 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
@@ -18391,12 +18391,12 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
@@ -18679,12 +18679,12 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
@@ -18967,12 +18967,12 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -19142,7 +19142,7 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
@@ -19255,12 +19255,12 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -19430,7 +19430,7 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
@@ -19543,12 +19543,12 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
@@ -19755,7 +19755,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>多頭排列股</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -19835,12 +19835,12 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>116</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -20010,7 +20010,7 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
@@ -20123,12 +20123,12 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>116</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -20298,7 +20298,7 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
@@ -20411,12 +20411,12 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>116</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -20586,7 +20586,7 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
@@ -20699,12 +20699,12 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>116</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
@@ -20987,12 +20987,12 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>116</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
@@ -21275,12 +21275,12 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>116</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -21450,7 +21450,7 @@
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
@@ -21563,12 +21563,12 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>116</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -21738,7 +21738,7 @@
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
@@ -21851,12 +21851,12 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>116</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -22026,7 +22026,7 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
@@ -22139,12 +22139,12 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>116</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -22314,7 +22314,7 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
@@ -22427,12 +22427,12 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>116</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -22602,7 +22602,7 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
@@ -22715,12 +22715,12 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>116</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -22890,7 +22890,7 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">

--- a/Result/checksun/水泥工業.xlsx
+++ b/Result/checksun/水泥工業.xlsx
@@ -1013,7 +1013,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -1301,7 +1305,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -1589,7 +1597,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -1877,7 +1889,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -2165,7 +2181,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -2453,7 +2473,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -2741,7 +2765,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -3029,7 +3057,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -3317,7 +3349,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -3605,7 +3641,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -4185,7 +4225,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -4473,7 +4517,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -4761,7 +4809,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -5049,7 +5101,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -5337,7 +5393,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -5625,7 +5685,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -5913,7 +5977,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -6201,7 +6269,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -6489,7 +6561,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -6777,7 +6853,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -7357,7 +7437,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -7645,7 +7729,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -7933,7 +8021,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -8221,7 +8313,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -8509,7 +8605,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -8797,7 +8897,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -9085,7 +9189,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -9373,7 +9481,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -9661,7 +9773,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -9949,7 +10065,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -10529,7 +10649,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -10817,7 +10941,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -11105,7 +11233,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -11393,7 +11525,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -11681,7 +11817,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -11969,7 +12109,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -12257,7 +12401,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -12545,7 +12693,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -12833,7 +12985,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -13121,7 +13277,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -13701,7 +13861,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -13989,7 +14153,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -14277,7 +14445,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -14565,7 +14737,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -14853,7 +15029,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -15141,7 +15321,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -15429,7 +15613,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -15717,7 +15905,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -16005,7 +16197,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -16293,7 +16489,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -16873,7 +17073,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -17161,7 +17365,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -17449,7 +17657,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -17737,7 +17949,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -18025,7 +18241,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -18313,7 +18533,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -18601,7 +18825,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -18889,7 +19117,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -19177,7 +19409,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -19465,7 +19701,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -20045,7 +20285,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -20333,7 +20577,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -20621,7 +20869,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -20909,7 +21161,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -21197,7 +21453,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -21485,7 +21745,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -21773,7 +22037,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -22061,7 +22329,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -22349,7 +22621,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -22637,7 +22913,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>2025-08-25</t>

--- a/Result/checksun/水泥工業.xlsx
+++ b/Result/checksun/水泥工業.xlsx
@@ -828,7 +828,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1078,67 +1078,67 @@
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.95760088156583</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-27.80643741672066</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.452574829745012</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.13</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.11%</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.80%</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥47.27%、預拌混凝土24.10%、房地產16.03%、爐石粉7.16%、租賃5.44% (2024年)</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 水泥成品</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -1445,67 +1445,67 @@
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.95760088156583</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-27.80643741672066</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.452574829745012</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.13</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.11%</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.80%</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥47.27%、預拌混凝土24.10%、房地產16.03%、爐石粉7.16%、租賃5.44% (2024年)</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 水泥成品</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>14.87</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1817,62 +1817,62 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.95760088156583</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-27.80643741672066</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.452574829745012</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.13</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.11%</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.80%</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥47.27%、預拌混凝土24.10%、房地產16.03%、爐石粉7.16%、租賃5.44% (2024年)</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 水泥成品</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1949,184 +1949,184 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>-17.00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>-2.76</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-17.00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-2.76</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-17.0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2025-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19.95</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>2025-05-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>-2.57</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>16.53</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>16.7675</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>17.209</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>-3.12</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>50.0000000000003</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>25.7575757575759</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>-17.65</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2025-03-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-03-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>20.25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>2025-05-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>-2.57</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>16.53</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>16.7675</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>17.209</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>-3.12</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>50.0000000000003</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>25.7575757575759</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>-17.65</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU5" t="inlineStr">
         <is>
           <t>2325196.2</t>
@@ -2179,67 +2179,67 @@
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.95760088156583</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-27.80643741672066</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.452574829745012</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.13</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.11%</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.80%</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥47.27%、預拌混凝土24.10%、房地產16.03%、爐石粉7.16%、租賃5.44% (2024年)</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2254,12 +2254,12 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 水泥成品</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -2546,67 +2546,67 @@
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.95760088156583</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-27.80643741672066</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.452574829745012</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.13</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.11%</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.80%</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥47.27%、預拌混凝土24.10%、房地產16.03%、爐石粉7.16%、租賃5.44% (2024年)</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 水泥成品</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2683,184 +2683,184 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>-18.50</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>-2.76</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2025-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>19.95</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>2025-05-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>-1.69</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>-1.40</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>-2.66</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>16.58</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>16.815</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>17.274</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>-12.28</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>-18.50</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>-2.76</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>1.960784313725523</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>-15.87</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2025-03-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-03-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>20.25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>2025-05-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>-1.69</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-1.40</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>-2.66</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>16.58</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>16.815</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>17.274</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>-12.28</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>1.960784313725523</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>-15.87</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU7" t="inlineStr">
         <is>
           <t>2587147.2</t>
@@ -2913,67 +2913,67 @@
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.95760088156583</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-27.80643741672066</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.452574829745012</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.13</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.11%</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.80%</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥47.27%、預拌混凝土24.10%、房地產16.03%、爐石粉7.16%、租賃5.44% (2024年)</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 水泥成品</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3050,12 +3050,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -3280,67 +3280,67 @@
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.95760088156583</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-27.80643741672066</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.452574829745012</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.13</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.11%</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.80%</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥47.27%、預拌混凝土24.10%、房地產16.03%、爐石粉7.16%、租賃5.44% (2024年)</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 水泥成品</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>17.94</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3417,184 +3417,184 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>-17.25</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>-2.76</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2025-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19.95</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>2025-05-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>-2.71</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>16.75</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>16.8725</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>17.343</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>-17.25</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>-2.76</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>6.666666666666761</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>9.85</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2025-03-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-03-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>20.25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>2025-05-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>-1.19</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>-2.71</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>16.75</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>16.8725</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>17.343</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>6.666666666666761</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>9.85</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU9" t="inlineStr">
         <is>
           <t>3027858.4</t>
@@ -3647,67 +3647,67 @@
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.95760088156583</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-27.80643741672066</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.452574829745012</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.13</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.11%</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.80%</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥47.27%、預拌混凝土24.10%、房地產16.03%、爐石粉7.16%、租賃5.44% (2024年)</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 水泥成品</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3784,184 +3784,184 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>-16.00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>-2.76</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>-16.00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>-2.76</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2025-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>19.95</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2025-05-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>-0.71</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>16.92</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>16.93</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>17.373</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>11.36</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>20.00000000000028</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>21.48148148148155</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>26.72</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2025-03-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-03-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>20.25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>2025-05-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-0.71</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>-2.55</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>16.92</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>17.373</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>11.36</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>20.00000000000028</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>21.48148148148155</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>26.72</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU10" t="inlineStr">
         <is>
           <t>3321624.0</t>
@@ -4019,62 +4019,62 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.95760088156583</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-27.80643741672066</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.452574829745012</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.13</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.11%</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.80%</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥47.27%、預拌混凝土24.10%、房地產16.03%、爐石粉7.16%、租賃5.44% (2024年)</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 水泥成品</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>7.90</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4151,184 +4151,184 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>-16.75</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>-2.76</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2025-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>19.95</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2025-05-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>-1.94</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>-2.40</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>16.98</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>16.98</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>17.397</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>12.07</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>-16.75</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>-2.76</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>27.77777777777782</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>15.90</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2025-03-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-03-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>20.25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>2025-05-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-1.94</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>-2.40</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>16.98</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>16.98</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>17.397</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>12.07</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>27.77777777777782</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>15.90</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU11" t="inlineStr">
         <is>
           <t>3611671.8</t>
@@ -4386,62 +4386,62 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.95760088156583</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-27.80643741672066</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.452574829745012</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.13</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.11%</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.80%</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥47.27%、預拌混凝土24.10%、房地產16.03%、爐石粉7.16%、租賃5.44% (2024年)</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 水泥成品</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -8248,109 +8248,109 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>2025-05-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15.2</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>2025-08-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>15.3</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>14.99</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>15.035</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>15.17</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>-20.45</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>2025-05-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025-05-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15.2</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>2025-08-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>15.5</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>15.3</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>-0.89</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>14.99</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>15.035</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>15.17</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>-20.45</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AR22" t="inlineStr">
         <is>
           <t>16.66666666666667</t>
@@ -8418,67 +8418,67 @@
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.712522243237496</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.974546986054468</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.991345496132694</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BK22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.30%</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.74%</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥及熟料45.33%、水泥34.83%、其他19.84% (2024年)</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -8615,109 +8615,109 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
+          <t>-7.0</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2025-05-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15.2</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>2025-08-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>15.3</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>-0.28</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>15.0425</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>15.177</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>-17.85</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>2025-05-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2025-05-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15.2</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>2025-08-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>15.5</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>15.3</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>-0.89</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>15.0425</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>15.177</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>-17.85</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AR23" t="inlineStr">
         <is>
           <t>33.33333333333334</t>
@@ -8790,62 +8790,62 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.712522243237496</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.974546986054468</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.991345496132694</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BK23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.30%</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.74%</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥及熟料45.33%、水泥34.83%、其他19.84% (2024年)</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -8982,7 +8982,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -9027,12 +9027,12 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -9157,62 +9157,62 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.712522243237496</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.974546986054468</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.991345496132694</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BK24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="BM24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.30%</t>
         </is>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.74%</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥及熟料45.33%、水泥34.83%、其他19.84% (2024年)</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="BT24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -9524,62 +9524,62 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.712522243237496</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.974546986054468</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.991345496132694</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BK25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="BM25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.30%</t>
         </is>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.74%</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥及熟料45.33%、水泥34.83%、其他19.84% (2024年)</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="BT25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -9761,12 +9761,12 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
@@ -9886,67 +9886,67 @@
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.712522243237496</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.974546986054468</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.991345496132694</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BK26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="BM26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.30%</t>
         </is>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.74%</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥及熟料45.33%、水泥34.83%、其他19.84% (2024年)</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="BT26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -10003,7 +10003,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -10258,62 +10258,62 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.712522243237496</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.974546986054468</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.991345496132694</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BK27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="BM27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.30%</t>
         </is>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.74%</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥及熟料45.33%、水泥34.83%、其他19.84% (2024年)</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -10328,12 +10328,12 @@
       </c>
       <c r="BT27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -10495,12 +10495,12 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -10625,62 +10625,62 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.712522243237496</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.974546986054468</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.991345496132694</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BK28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="BM28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.30%</t>
         </is>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.74%</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥及熟料45.33%、水泥34.83%、其他19.84% (2024年)</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="BT28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
@@ -10987,67 +10987,67 @@
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.712522243237496</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.974546986054468</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.991345496132694</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BK29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BL29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="BM29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.30%</t>
         </is>
       </c>
       <c r="BN29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.74%</t>
         </is>
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥及熟料45.33%、水泥34.83%、其他19.84% (2024年)</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -11062,12 +11062,12 @@
       </c>
       <c r="BT29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="BU29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -11229,12 +11229,12 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
@@ -11359,62 +11359,62 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.712522243237496</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.974546986054468</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.991345496132694</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BK30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BL30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="BM30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.30%</t>
         </is>
       </c>
       <c r="BN30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.74%</t>
         </is>
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥及熟料45.33%、水泥34.83%、其他19.84% (2024年)</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -11429,12 +11429,12 @@
       </c>
       <c r="BT30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="BU30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -11596,12 +11596,12 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -11726,62 +11726,62 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.712522243237496</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.974546986054468</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.991345496132694</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BK31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BL31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="BM31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.30%</t>
         </is>
       </c>
       <c r="BN31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.74%</t>
         </is>
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥及熟料45.33%、水泥34.83%、其他19.84% (2024年)</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -11796,12 +11796,12 @@
       </c>
       <c r="BT31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="BU31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -22848,7 +22848,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -22868,7 +22868,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -22918,7 +22918,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -22928,109 +22928,109 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>34.8</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>33.45</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>23.75</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>-1.36</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>-1.71</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>22.86</t>
+        </is>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>23.2575</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>23.057</t>
+        </is>
+      </c>
+      <c r="AN62" t="inlineStr">
+        <is>
+          <t>-128.48</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2025-02-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>33.45</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD62" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="AE62" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="AF62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>22.86</t>
-        </is>
-      </c>
-      <c r="AL62" t="inlineStr">
-        <is>
-          <t>23.2575</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>23.057</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>-128.48</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="AP62" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AQ62" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AR62" t="inlineStr">
         <is>
           <t>3.703703703703719</t>
@@ -23098,67 +23098,67 @@
       </c>
       <c r="BE62" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BJ62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR62" t="inlineStr">
@@ -23173,12 +23173,12 @@
       </c>
       <c r="BT62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -23215,7 +23215,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -23235,7 +23235,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -23285,7 +23285,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -23295,109 +23295,109 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>34.8</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>33.45</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>23.75</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>-1.70</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>22.93</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>23.3275</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>23.082</t>
+        </is>
+      </c>
+      <c r="AN63" t="inlineStr">
+        <is>
+          <t>-146.09</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2025-02-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>33.45</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD63" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>-0.57</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>-1.70</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>22.93</t>
-        </is>
-      </c>
-      <c r="AL63" t="inlineStr">
-        <is>
-          <t>23.3275</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>23.082</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>-146.09</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="AP63" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AQ63" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AR63" t="inlineStr">
         <is>
           <t>14.81481481481492</t>
@@ -23470,62 +23470,62 @@
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="BJ63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR63" t="inlineStr">
@@ -23540,12 +23540,12 @@
       </c>
       <c r="BT63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -23582,7 +23582,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -23602,7 +23602,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -23652,7 +23652,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -23662,7 +23662,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -23707,12 +23707,12 @@
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="AH64" t="inlineStr">
@@ -23837,62 +23837,62 @@
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR64" t="inlineStr">
@@ -23907,12 +23907,12 @@
       </c>
       <c r="BT64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -23949,7 +23949,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -23969,7 +23969,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -24019,7 +24019,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -24029,7 +24029,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -24074,12 +24074,12 @@
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="AH65" t="inlineStr">
@@ -24204,62 +24204,62 @@
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BJ65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR65" t="inlineStr">
@@ -24274,12 +24274,12 @@
       </c>
       <c r="BT65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -24316,7 +24316,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -24336,7 +24336,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -24396,7 +24396,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-9.0</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -24441,12 +24441,12 @@
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="AH66" t="inlineStr">
@@ -24571,62 +24571,62 @@
       </c>
       <c r="BF66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BJ66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR66" t="inlineStr">
@@ -24641,12 +24641,12 @@
       </c>
       <c r="BT66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -24683,7 +24683,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>12.89</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -24703,7 +24703,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -24753,7 +24753,7 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -24763,109 +24763,109 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>34.8</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>33.45</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>23.75</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>-1.73</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>23.09</t>
+        </is>
+      </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>23.4975</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>23.216</t>
+        </is>
+      </c>
+      <c r="AN67" t="inlineStr">
+        <is>
+          <t>-357.75</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2025-02-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>33.45</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>-1.73</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>23.09</t>
-        </is>
-      </c>
-      <c r="AL67" t="inlineStr">
-        <is>
-          <t>23.4975</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>23.216</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>-357.75</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AP67" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AR67" t="inlineStr">
         <is>
           <t>35.41666666666675</t>
@@ -24933,67 +24933,67 @@
       </c>
       <c r="BE67" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="BJ67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR67" t="inlineStr">
@@ -25008,12 +25008,12 @@
       </c>
       <c r="BT67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -25070,7 +25070,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -25120,7 +25120,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -25175,12 +25175,12 @@
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="AH68" t="inlineStr">
@@ -25305,62 +25305,62 @@
       </c>
       <c r="BF68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BJ68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR68" t="inlineStr">
@@ -25375,12 +25375,12 @@
       </c>
       <c r="BT68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -25417,7 +25417,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>17.58</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -25487,7 +25487,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -25497,7 +25497,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="AH69" t="inlineStr">
@@ -25667,67 +25667,67 @@
       </c>
       <c r="BE69" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BJ69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR69" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="BT69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -25784,7 +25784,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -25804,7 +25804,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -25909,12 +25909,12 @@
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="AH70" t="inlineStr">
@@ -26039,62 +26039,62 @@
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BJ70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR70" t="inlineStr">
@@ -26109,12 +26109,12 @@
       </c>
       <c r="BT70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -26151,7 +26151,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -26171,7 +26171,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -26276,12 +26276,12 @@
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="AH71" t="inlineStr">
@@ -26406,62 +26406,62 @@
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BJ71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR71" t="inlineStr">
@@ -26476,12 +26476,12 @@
       </c>
       <c r="BT71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>

--- a/Result/checksun/水泥工業.xlsx
+++ b/Result/checksun/水泥工業.xlsx
@@ -1011,15 +1011,11 @@
           <t>16.7375</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>17.08</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>17.465</t>
-        </is>
+      <c r="AN2" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>17.465</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -1398,15 +1394,11 @@
           <t>16.7325</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>17.104</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>17.501875</t>
-        </is>
+      <c r="AN3" t="n">
+        <v>17.104</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>17.501875</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -1785,15 +1777,11 @@
           <t>16.7475</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>17.131</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>17.54</t>
-        </is>
+      <c r="AN4" t="n">
+        <v>17.131</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>17.54</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -2172,15 +2160,11 @@
           <t>16.7675</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>17.16</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>17.58</t>
-        </is>
+      <c r="AN5" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>17.58</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -2559,15 +2543,11 @@
           <t>16.7625</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>17.18</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>17.619375</t>
-        </is>
+      <c r="AN6" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>17.619375</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -2946,15 +2926,11 @@
           <t>16.7675</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>17.209</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>17.6575</t>
-        </is>
+      <c r="AN7" t="n">
+        <v>17.209</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>17.6575</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -3333,15 +3309,11 @@
           <t>16.7925</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>17.241</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>17.69375</t>
-        </is>
+      <c r="AN8" t="n">
+        <v>17.241</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>17.69375</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -3720,15 +3692,11 @@
           <t>16.815</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>17.274</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>17.73375</t>
-        </is>
+      <c r="AN9" t="n">
+        <v>17.274</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>17.73375</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -4107,15 +4075,11 @@
           <t>16.8475</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>17.312</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>17.77625</t>
-        </is>
+      <c r="AN10" t="n">
+        <v>17.312</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>17.77625</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -4494,15 +4458,11 @@
           <t>16.8725</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>17.343</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>17.81125</t>
-        </is>
+      <c r="AN11" t="n">
+        <v>17.343</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>17.81125</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -4881,15 +4841,11 @@
           <t>15.62</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>15.72</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>15.90375</t>
-        </is>
+      <c r="AN12" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>15.90375</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -5268,15 +5224,11 @@
           <t>15.63</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>15.731</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>15.92125</t>
-        </is>
+      <c r="AN13" t="n">
+        <v>15.731</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>15.92125</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -5655,15 +5607,11 @@
           <t>15.6325</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>15.742</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>15.9375</t>
-        </is>
+      <c r="AN14" t="n">
+        <v>15.742</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>15.9375</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -6042,15 +5990,11 @@
           <t>15.635</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>15.749</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>15.95375</t>
-        </is>
+      <c r="AN15" t="n">
+        <v>15.749</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>15.95375</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
@@ -6429,15 +6373,11 @@
           <t>15.6375</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>15.757</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>15.969375</t>
-        </is>
+      <c r="AN16" t="n">
+        <v>15.757</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>15.969375</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
@@ -6816,15 +6756,11 @@
           <t>15.6375</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>15.765</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>15.984375</t>
-        </is>
+      <c r="AN17" t="n">
+        <v>15.765</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>15.984375</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -7203,15 +7139,11 @@
           <t>15.6425</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>15.774</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>15.99875</t>
-        </is>
+      <c r="AN18" t="n">
+        <v>15.774</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>15.99875</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -7590,15 +7522,11 @@
           <t>15.645</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>15.779</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>16.013125</t>
-        </is>
+      <c r="AN19" t="n">
+        <v>15.779</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>16.013125</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -7977,15 +7905,11 @@
           <t>15.65</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>15.789</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>16.02875</t>
-        </is>
+      <c r="AN20" t="n">
+        <v>15.789</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>16.02875</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -8364,15 +8288,11 @@
           <t>15.655</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>15.797</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>16.045</t>
-        </is>
+      <c r="AN21" t="n">
+        <v>15.797</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>16.045</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -8751,15 +8671,11 @@
           <t>15.0175</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>15.149</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>14.94625</t>
-        </is>
+      <c r="AN22" t="n">
+        <v>15.149</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>14.94625</v>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
@@ -9138,15 +9054,11 @@
           <t>15.03</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>15.161</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>14.945</t>
-        </is>
+      <c r="AN23" t="n">
+        <v>15.161</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>14.945</v>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
@@ -9525,15 +9437,11 @@
           <t>15.035</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>15.17</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>14.944375</t>
-        </is>
+      <c r="AN24" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>14.944375</v>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -9912,15 +9820,11 @@
           <t>15.0425</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>15.177</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>14.945</t>
-        </is>
+      <c r="AN25" t="n">
+        <v>15.177</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>14.945</v>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -10299,15 +10203,11 @@
           <t>15.0475</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>15.179</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>14.944375</t>
-        </is>
+      <c r="AN26" t="n">
+        <v>15.179</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>14.944375</v>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
@@ -10686,15 +10586,11 @@
           <t>15.05</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>15.182</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>14.943125</t>
-        </is>
+      <c r="AN27" t="n">
+        <v>15.182</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>14.943125</v>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -11073,15 +10969,11 @@
           <t>15.0525</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>15.172</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>14.940625</t>
-        </is>
+      <c r="AN28" t="n">
+        <v>15.172</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>14.940625</v>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
@@ -11460,15 +11352,11 @@
           <t>15.0525</t>
         </is>
       </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>15.155</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>14.938125</t>
-        </is>
+      <c r="AN29" t="n">
+        <v>15.155</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>14.938125</v>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
@@ -11847,15 +11735,11 @@
           <t>15.055</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>15.139</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>14.936875</t>
-        </is>
+      <c r="AN30" t="n">
+        <v>15.139</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>14.936875</v>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
@@ -12234,15 +12118,11 @@
           <t>15.0575</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>15.123</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>14.935</t>
-        </is>
+      <c r="AN31" t="n">
+        <v>15.123</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>14.935</v>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
@@ -12621,15 +12501,11 @@
           <t>31.1325</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>30.331</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>29.169375</t>
-        </is>
+      <c r="AN32" t="n">
+        <v>30.331</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>29.169375</v>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
@@ -13008,15 +12884,11 @@
           <t>31.115</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>30.278</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>29.130625</t>
-        </is>
+      <c r="AN33" t="n">
+        <v>30.278</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>29.130625</v>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
@@ -13395,15 +13267,11 @@
           <t>31.0575</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>30.209</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>29.086875</t>
-        </is>
+      <c r="AN34" t="n">
+        <v>30.209</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>29.086875</v>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
@@ -13782,15 +13650,11 @@
           <t>31.02</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>30.129</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>29.044375</t>
-        </is>
+      <c r="AN35" t="n">
+        <v>30.129</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>29.044375</v>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
@@ -14169,15 +14033,11 @@
           <t>30.9375</t>
         </is>
       </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>30.03</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>28.99625</t>
-        </is>
+      <c r="AN36" t="n">
+        <v>30.03</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>28.99625</v>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
@@ -14556,15 +14416,11 @@
           <t>30.8125</t>
         </is>
       </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>28.943125</t>
-        </is>
+      <c r="AN37" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>28.943125</v>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
@@ -14943,15 +14799,11 @@
           <t>30.6825</t>
         </is>
       </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>29.806</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>28.885625</t>
-        </is>
+      <c r="AN38" t="n">
+        <v>29.806</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>28.885625</v>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
@@ -15330,15 +15182,11 @@
           <t>30.5425</t>
         </is>
       </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>29.69</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>28.829375</t>
-        </is>
+      <c r="AN39" t="n">
+        <v>29.69</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>28.829375</v>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
@@ -15717,15 +15565,11 @@
           <t>30.3975</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>29.57</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>28.771875</t>
-        </is>
+      <c r="AN40" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>28.771875</v>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
@@ -16104,15 +15948,11 @@
           <t>30.3125</t>
         </is>
       </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>29.476</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>28.726875</t>
-        </is>
+      <c r="AN41" t="n">
+        <v>29.476</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>28.726875</v>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
@@ -16491,15 +16331,11 @@
           <t>13.2</t>
         </is>
       </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>13.313</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>13.59875</t>
-        </is>
+      <c r="AN42" t="n">
+        <v>13.313</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>13.59875</v>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
@@ -16878,15 +16714,11 @@
           <t>13.2375</t>
         </is>
       </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>13.326</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>13.62</t>
-        </is>
+      <c r="AN43" t="n">
+        <v>13.326</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>13.62</v>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
@@ -17265,15 +17097,11 @@
           <t>13.265</t>
         </is>
       </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>13.34</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>13.639375</t>
-        </is>
+      <c r="AN44" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>13.639375</v>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
@@ -17652,15 +17480,11 @@
           <t>13.2925</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>13.352</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>13.660625</t>
-        </is>
+      <c r="AN45" t="n">
+        <v>13.352</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>13.660625</v>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
@@ -18039,15 +17863,11 @@
           <t>13.305</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>13.363</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>13.679375</t>
-        </is>
+      <c r="AN46" t="n">
+        <v>13.363</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>13.679375</v>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
@@ -18426,15 +18246,11 @@
           <t>13.315</t>
         </is>
       </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>13.371</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>13.6975</t>
-        </is>
+      <c r="AN47" t="n">
+        <v>13.371</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>13.6975</v>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
@@ -18813,15 +18629,11 @@
           <t>13.33</t>
         </is>
       </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>13.381</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>13.714375</t>
-        </is>
+      <c r="AN48" t="n">
+        <v>13.381</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>13.714375</v>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
@@ -19200,15 +19012,11 @@
           <t>13.34</t>
         </is>
       </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>13.393</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>13.731875</t>
-        </is>
+      <c r="AN49" t="n">
+        <v>13.393</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>13.731875</v>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
@@ -19587,15 +19395,11 @@
           <t>13.3425</t>
         </is>
       </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>13.407</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>13.749375</t>
-        </is>
+      <c r="AN50" t="n">
+        <v>13.407</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>13.749375</v>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
@@ -19974,15 +19778,11 @@
           <t>13.345</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>13.42</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>13.764375</t>
-        </is>
+      <c r="AN51" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>13.764375</v>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
@@ -20361,15 +20161,11 @@
           <t>36.94</t>
         </is>
       </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>36.943</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>38.154375</t>
-        </is>
+      <c r="AN52" t="n">
+        <v>36.943</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>38.154375</v>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
@@ -20748,15 +20544,11 @@
           <t>37.03250000000001</t>
         </is>
       </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>37.0</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>38.22875000000001</t>
-        </is>
+      <c r="AN53" t="n">
+        <v>37</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>38.22875000000001</v>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
@@ -21135,15 +20927,11 @@
           <t>37.0675</t>
         </is>
       </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>37.059</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>38.31124999999999</t>
-        </is>
+      <c r="AN54" t="n">
+        <v>37.059</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>38.31124999999999</v>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
@@ -21522,15 +21310,11 @@
           <t>37.1125</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>37.131</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>38.40625</t>
-        </is>
+      <c r="AN55" t="n">
+        <v>37.131</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>38.40625</v>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
@@ -21909,15 +21693,11 @@
           <t>37.1425</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>37.191</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>38.4875</t>
-        </is>
+      <c r="AN56" t="n">
+        <v>37.191</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>38.4875</v>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
@@ -22296,15 +22076,11 @@
           <t>37.135</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>37.23699999999999</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>38.566875</t>
-        </is>
+      <c r="AN57" t="n">
+        <v>37.23699999999999</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>38.566875</v>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
@@ -22683,15 +22459,11 @@
           <t>37.105</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>37.275</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>38.629375</t>
-        </is>
+      <c r="AN58" t="n">
+        <v>37.275</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>38.629375</v>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
@@ -23070,15 +22842,11 @@
           <t>37.0575</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>37.334</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>38.7025</t>
-        </is>
+      <c r="AN59" t="n">
+        <v>37.334</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>38.7025</v>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
@@ -23457,15 +23225,11 @@
           <t>37.0075</t>
         </is>
       </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>37.402</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>38.773125</t>
-        </is>
+      <c r="AN60" t="n">
+        <v>37.402</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>38.773125</v>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
@@ -23844,15 +23608,11 @@
           <t>36.975</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>37.472</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>38.84</t>
-        </is>
+      <c r="AN61" t="n">
+        <v>37.472</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>38.84</v>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
@@ -24231,15 +23991,11 @@
           <t>23.0875</t>
         </is>
       </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>22.993</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>23.395625</t>
-        </is>
+      <c r="AN62" t="n">
+        <v>22.993</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>23.395625</v>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
@@ -24618,15 +24374,11 @@
           <t>23.1825</t>
         </is>
       </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>23.029</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>23.43</t>
-        </is>
+      <c r="AN63" t="n">
+        <v>23.029</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>23.43</v>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
@@ -25005,15 +24757,11 @@
           <t>23.2575</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>23.057</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>23.46375</t>
-        </is>
+      <c r="AN64" t="n">
+        <v>23.057</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>23.46375</v>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
@@ -25392,15 +25140,11 @@
           <t>23.3275</t>
         </is>
       </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>23.082</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>23.49875</t>
-        </is>
+      <c r="AN65" t="n">
+        <v>23.082</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>23.49875</v>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
@@ -25779,15 +25523,11 @@
           <t>23.36</t>
         </is>
       </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>23.121</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>23.529375</t>
-        </is>
+      <c r="AN66" t="n">
+        <v>23.121</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>23.529375</v>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
@@ -26166,15 +25906,11 @@
           <t>23.4</t>
         </is>
       </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>23.157</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>23.569375</t>
-        </is>
+      <c r="AN67" t="n">
+        <v>23.157</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>23.569375</v>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
@@ -26553,15 +26289,11 @@
           <t>23.4775</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>23.188</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>23.6</t>
-        </is>
+      <c r="AN68" t="n">
+        <v>23.188</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>23.6</v>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
@@ -26940,15 +26672,11 @@
           <t>23.4975</t>
         </is>
       </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>23.216</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>23.640625</t>
-        </is>
+      <c r="AN69" t="n">
+        <v>23.216</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>23.640625</v>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
@@ -27327,15 +27055,11 @@
           <t>23.4625</t>
         </is>
       </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>23.244</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>23.676875</t>
-        </is>
+      <c r="AN70" t="n">
+        <v>23.244</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>23.676875</v>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
@@ -27714,15 +27438,11 @@
           <t>23.41</t>
         </is>
       </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>23.26600000000001</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>23.7075</t>
-        </is>
+      <c r="AN71" t="n">
+        <v>23.26600000000001</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>23.7075</v>
       </c>
       <c r="AP71" t="inlineStr">
         <is>

--- a/Result/checksun/水泥工業.xlsx
+++ b/Result/checksun/水泥工業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1725,7 +1725,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2149,7 +2149,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>1110</t>
@@ -2571,7 +2575,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>1110</t>
@@ -2995,7 +3003,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3419,7 +3427,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>1110</t>
@@ -3841,7 +3853,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>1110</t>
@@ -4263,7 +4279,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>1110</t>
@@ -4685,7 +4705,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>1110</t>
@@ -5107,7 +5131,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>1110</t>
@@ -5531,7 +5559,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5961,7 +5989,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6391,7 +6419,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6821,7 +6849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7251,7 +7279,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7681,7 +7709,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8111,7 +8139,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8539,7 +8567,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>1109</t>
@@ -8965,7 +8997,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>1109</t>
@@ -10253,7 +10289,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10683,7 +10719,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11113,7 +11149,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11543,7 +11579,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11973,7 +12009,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12403,7 +12439,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12833,7 +12869,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13263,7 +13299,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13693,7 +13729,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14121,7 +14157,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>1108</t>
@@ -14547,7 +14587,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>1108</t>
@@ -16683,7 +16727,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -23104,7 +23148,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23533,7 +23577,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -23962,7 +24006,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -27815,7 +27859,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28243,7 +28287,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28671,7 +28715,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29099,7 +29143,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29529,7 +29573,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -29959,7 +30003,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30389,7 +30433,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -30819,7 +30863,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31249,7 +31293,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -31677,7 +31721,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>1101</t>
@@ -32103,7 +32151,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>1101</t>

--- a/Result/checksun/水泥工業.xlsx
+++ b/Result/checksun/水泥工業.xlsx
@@ -1008,32 +1008,32 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-26 00:00:00</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-29 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-12 00:00:00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-05 00:00:00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1058,22 +1058,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.29</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/27</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2025-04-07 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-113.87</t>
+          <t>-108.70</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>5851208.910358566</t>
+          <t>9471004.564960629</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-287459.6716178061</t>
+          <t>-287459.6716178097</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-493784.5518211471</t>
+          <t>-493784.551821148</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -1509,32 +1509,32 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-26 00:00:00</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-29 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-12 00:00:00</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-05 00:00:00</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1559,22 +1559,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-29.17</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/27</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2025-04-07 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-113.42</t>
+          <t>-108.43</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>5851208.910358566</t>
+          <t>9471004.564960629</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-249946.0570353805</t>
+          <t>-249946.0570353846</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-504043.4995978284</t>
+          <t>-504043.4995978293</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -2010,32 +2010,32 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-26 00:00:00</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-29 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-12 00:00:00</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-05 00:00:00</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2045,12 +2045,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -2060,22 +2060,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-30.26</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/07</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/27</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2025-04-07 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-112.02</t>
+          <t>-107.54</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>5851208.910358566</t>
+          <t>9471004.564960629</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-203746.5220240263</t>
+          <t>-203746.522024031</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-417773.9428645927</t>
+          <t>-417773.9428645936</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2439,12 +2439,12 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-26 00:00:00</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-29 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-12 00:00:00</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-05 00:00:00</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -2561,22 +2561,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.73</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/07</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/27</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2025-04-07 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-110.26</t>
+          <t>-106.44</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>5851208.910358566</t>
+          <t>9471004.564960629</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-164832.4455075596</t>
+          <t>-164832.4455075651</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-733211.5424290919</t>
+          <t>-733211.5424290933</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -3012,32 +3012,32 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-26 00:00:00</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-29 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-12 00:00:00</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-05 00:00:00</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -3062,22 +3062,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.95</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/07</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3102,12 +3102,12 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/27</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2025-04-07 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -3225,12 +3225,12 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-109.36</t>
+          <t>-105.88</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>5851208.910358566</t>
+          <t>9471004.564960629</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-61490.7915218265</t>
+          <t>-61490.79152183271</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-680141.0938630523</t>
+          <t>-680141.0938630537</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -3513,32 +3513,32 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-26 00:00:00</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-29 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-12 00:00:00</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-05 00:00:00</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -3563,22 +3563,22 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-29.17</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/07</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/27</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2025-04-07 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-108.21</t>
+          <t>-105.15</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>5851208.910358566</t>
+          <t>9471004.564960629</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>50991.08163112364</t>
+          <t>50991.08163111657</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-601249.485416458</t>
+          <t>-601249.4854164599</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -4014,32 +4014,32 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-26 00:00:00</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-29 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-12 00:00:00</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-05 00:00:00</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -4064,22 +4064,22 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.73</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/27</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2025-04-07 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-107.03</t>
+          <t>-104.41</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>5851208.910358566</t>
+          <t>9471004.564960629</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>169580.2756397749</t>
+          <t>169580.2756397668</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-550027.6345850215</t>
+          <t>-550027.6345850234</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -4515,32 +4515,32 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-26 00:00:00</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-29 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-12 00:00:00</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-05 00:00:00</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -4565,22 +4565,22 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.73</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -4605,12 +4605,12 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/27</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2025-04-07 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-106.18</t>
+          <t>-103.88</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>5851208.910358566</t>
+          <t>9471004.564960629</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>300418.0774988288</t>
+          <t>300418.0774988196</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-334553.9678763617</t>
+          <t>-334553.9678763635</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4944,12 +4944,12 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -5016,32 +5016,32 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-26 00:00:00</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-29 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-12 00:00:00</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-05 00:00:00</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -5066,22 +5066,22 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.95</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/27</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2025-04-07 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-105.46</t>
+          <t>-103.43</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>5851208.910358566</t>
+          <t>9471004.564960629</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>415867.5402943179</t>
+          <t>415867.5402943075</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-204101.4094398348</t>
+          <t>-204101.4094398366</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -5517,32 +5517,32 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-26 00:00:00</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-29 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-12 00:00:00</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-05 00:00:00</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -5567,22 +5567,22 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/27</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2025-04-07 00:00:00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -5730,12 +5730,12 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-105.03</t>
+          <t>-103.16</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>5851208.910358566</t>
+          <t>9471004.564960629</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>528589.1675187093</t>
+          <t>528589.1675186973</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>65935.4743780559</t>
+          <t>65935.4743780531</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -6018,32 +6018,32 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-26 00:00:00</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-29 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-12 00:00:00</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-08-05 00:00:00</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/27</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2025-04-07 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -6231,12 +6231,12 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-105.35</t>
+          <t>-103.36</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>5851208.910358566</t>
+          <t>9471004.564960629</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>612708.02081701</t>
+          <t>612708.0208169962</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>477077.255747254</t>
+          <t>477077.2557472512</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CY12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -6519,32 +6519,32 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-06 00:00:00</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-12 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-05 00:00:00</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-18 00:00:00</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -6554,12 +6554,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.53</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-113.36</t>
+          <t>-105.66</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-1650.654739491101</t>
+          <t>-1650.654739498319</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-109354.2346517846</t>
+          <t>-109354.234651786</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="CY13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -7024,32 +7024,32 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-06 00:00:00</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-12 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-05 00:00:00</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-18 00:00:00</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.80</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-112.92</t>
+          <t>-105.48</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -7282,12 +7282,12 @@
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>17931.81433547136</t>
+          <t>17931.81433546308</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-49249.71590493829</t>
+          <t>-49249.71590493969</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="CY14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -7529,32 +7529,32 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-06 00:00:00</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-12 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-05 00:00:00</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-18 00:00:00</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -7564,12 +7564,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-112.64</t>
+          <t>-105.36</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>30146.63801554585</t>
+          <t>30146.63801553632</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-19585.05641283817</t>
+          <t>-19585.0564128398</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -7962,12 +7962,12 @@
       </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="CY15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -8034,32 +8034,32 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-06 00:00:00</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-12 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-05 00:00:00</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-18 00:00:00</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -8251,12 +8251,12 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-113.45</t>
+          <t>-105.70</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>39188.76427525203</t>
+          <t>39188.76427524107</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-52467.39798080828</t>
+          <t>-52467.39798081038</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="CY16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -8539,32 +8539,32 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-06 00:00:00</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-12 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-05 00:00:00</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-18 00:00:00</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -8574,12 +8574,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.99</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-114.44</t>
+          <t>-106.12</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -8797,12 +8797,12 @@
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>55853.52104908118</t>
+          <t>55853.52104906861</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-28235.44315002207</t>
+          <t>-28235.44315002463</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="CY17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-06 00:00:00</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-12 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-05 00:00:00</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-18 00:00:00</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.99</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -9261,12 +9261,12 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-115.67</t>
+          <t>-106.64</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -9302,12 +9302,12 @@
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>71142.42363073632</t>
+          <t>71142.42363072193</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-80307.6704221128</t>
+          <t>-80307.6704221156</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="CY18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -9549,32 +9549,32 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-06 00:00:00</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-12 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-05 00:00:00</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-18 00:00:00</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-116.46</t>
+          <t>-106.98</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -9807,12 +9807,12 @@
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>98678.80436761798</t>
+          <t>98678.80436760146</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-63218.72115288116</t>
+          <t>-63218.72115288442</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="CY19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -10054,32 +10054,32 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-06 00:00:00</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-12 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-05 00:00:00</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-18 00:00:00</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -10104,12 +10104,12 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.53</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-116.54</t>
+          <t>-107.01</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
@@ -10312,12 +10312,12 @@
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>128114.7180986178</t>
+          <t>128114.7180985989</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>2532.017844338436</t>
+          <t>2532.01784433471</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="CX20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="CY20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -10559,32 +10559,32 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-06 00:00:00</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-12 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-05 00:00:00</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-18 00:00:00</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -10594,12 +10594,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -10609,12 +10609,12 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.53</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-116.31</t>
+          <t>-106.91</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
@@ -10817,12 +10817,12 @@
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>150947.9363266686</t>
+          <t>150947.9363266469</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>120719.7514887829</t>
+          <t>120719.7514887787</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -10992,12 +10992,12 @@
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="CY21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -11064,32 +11064,32 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-06 00:00:00</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-12 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-05 00:00:00</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-18 00:00:00</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -11114,12 +11114,12 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-116.45</t>
+          <t>-106.97</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -11296,7 +11296,7 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>156443.9699335569</t>
+          <t>156443.9699335321</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>91101.55842767563</t>
+          <t>91101.5584276705</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="CY22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -11569,32 +11569,32 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-06 00:00:00</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-12 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-05 00:00:00</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-18 00:00:00</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -11619,12 +11619,12 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-04-08 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
@@ -11786,12 +11786,12 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-117.22</t>
+          <t>-107.30</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>2673191.970119522</t>
+          <t>6036851.568897638</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
@@ -11827,12 +11827,12 @@
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>168324.4083891717</t>
+          <t>168324.4083891432</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>129697.1555393911</t>
+          <t>129697.155539385</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="CX23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="CY23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -12069,37 +12069,37 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-18 00:00:00</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-07 00:00:00</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
@@ -12291,12 +12291,12 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-87.17</t>
+          <t>-88.22</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>21381.35805974964</t>
+          <t>21381.35805974701</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-339637.0314707565</t>
+          <t>-339637.031470757</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="CP24" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ24" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="CX24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="CY24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
@@ -12574,37 +12574,37 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-18 00:00:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-07 00:00:00</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -12699,7 +12699,7 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
@@ -12796,12 +12796,12 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-86.52</t>
+          <t>-87.62</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>87021.0652471144</t>
+          <t>87021.06524711137</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-250527.5853005182</t>
+          <t>-250527.5853005187</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="CP25" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ25" t="inlineStr">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="CX25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -13079,37 +13079,37 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-18 00:00:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-07 00:00:00</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -13119,12 +13119,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -13134,12 +13134,12 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-85.57</t>
+          <t>-86.75</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
@@ -13342,12 +13342,12 @@
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>148393.5471648658</t>
+          <t>148393.5471648623</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-138084.7841537301</t>
+          <t>-138084.7841537306</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
@@ -13477,7 +13477,7 @@
       </c>
       <c r="CP26" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ26" t="inlineStr">
@@ -13517,12 +13517,12 @@
       </c>
       <c r="CX26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -13584,37 +13584,37 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-18 00:00:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-07 00:00:00</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-84.67</t>
+          <t>-85.92</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
@@ -13847,12 +13847,12 @@
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>200480.5164955196</t>
+          <t>200480.5164955156</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-63954.82593854284</t>
+          <t>-63954.8259385433</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
@@ -13982,7 +13982,7 @@
       </c>
       <c r="CP27" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ27" t="inlineStr">
@@ -14022,12 +14022,12 @@
       </c>
       <c r="CX27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -14089,37 +14089,37 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-18 00:00:00</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-07 00:00:00</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -14144,12 +14144,12 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
@@ -14311,12 +14311,12 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-84.37</t>
+          <t>-85.65</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
@@ -14352,12 +14352,12 @@
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>248559.6696653491</t>
+          <t>248559.6696653445</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-172887.8561333278</t>
+          <t>-172887.8561333283</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="CP28" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ28" t="inlineStr">
@@ -14527,12 +14527,12 @@
       </c>
       <c r="CX28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -14594,37 +14594,37 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-18 00:00:00</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-07 00:00:00</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -14634,12 +14634,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -14649,12 +14649,12 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
@@ -14816,12 +14816,12 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>-85.00</t>
+          <t>-86.22</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
@@ -14831,7 +14831,7 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
@@ -14857,12 +14857,12 @@
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>325186.4925378358</t>
+          <t>325186.4925378304</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
-          <t>-76061.04726397293</t>
+          <t>-76061.04726397339</t>
         </is>
       </c>
       <c r="BQ29" t="inlineStr">
@@ -14992,7 +14992,7 @@
       </c>
       <c r="CP29" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ29" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="CX29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -15099,37 +15099,37 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-18 00:00:00</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-07 00:00:00</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -15139,12 +15139,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -15154,12 +15154,12 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>-86.00</t>
+          <t>-87.14</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
@@ -15336,7 +15336,7 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>398140.5906836192</t>
+          <t>398140.5906836129</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
-          <t>136299.9313802477</t>
+          <t>136299.9313802472</t>
         </is>
       </c>
       <c r="BQ30" t="inlineStr">
@@ -15497,7 +15497,7 @@
       </c>
       <c r="CP30" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ30" t="inlineStr">
@@ -15537,12 +15537,12 @@
       </c>
       <c r="CX30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -15604,37 +15604,37 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-18 00:00:00</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-07 00:00:00</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -15644,12 +15644,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -15659,12 +15659,12 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -15729,7 +15729,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
@@ -15826,12 +15826,12 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>-86.96</t>
+          <t>-88.02</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
@@ -15841,7 +15841,7 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
@@ -15867,12 +15867,12 @@
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>445747.9832842322</t>
+          <t>445747.9832842249</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
-          <t>93841.83189412626</t>
+          <t>93841.83189412532</t>
         </is>
       </c>
       <c r="BQ31" t="inlineStr">
@@ -16002,7 +16002,7 @@
       </c>
       <c r="CP31" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ31" t="inlineStr">
@@ -16042,12 +16042,12 @@
       </c>
       <c r="CX31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
@@ -16109,37 +16109,37 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-18 00:00:00</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-07 00:00:00</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -16149,12 +16149,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -16164,12 +16164,12 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
@@ -16331,12 +16331,12 @@
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>-88.23</t>
+          <t>-89.19</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr">
@@ -16372,12 +16372,12 @@
       </c>
       <c r="BO32" t="inlineStr">
         <is>
-          <t>509730.9199006151</t>
+          <t>509730.9199006066</t>
         </is>
       </c>
       <c r="BP32" t="inlineStr">
         <is>
-          <t>299804.0886320192</t>
+          <t>299804.0886320183</t>
         </is>
       </c>
       <c r="BQ32" t="inlineStr">
@@ -16507,7 +16507,7 @@
       </c>
       <c r="CP32" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ32" t="inlineStr">
@@ -16547,12 +16547,12 @@
       </c>
       <c r="CX32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
@@ -16614,37 +16614,37 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-18 00:00:00</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-07 00:00:00</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -16654,12 +16654,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -16669,12 +16669,12 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -16739,7 +16739,7 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
@@ -16836,12 +16836,12 @@
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>-89.83</t>
+          <t>-90.66</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr">
@@ -16877,12 +16877,12 @@
       </c>
       <c r="BO33" t="inlineStr">
         <is>
-          <t>547899.4346767234</t>
+          <t>547899.4346767135</t>
         </is>
       </c>
       <c r="BP33" t="inlineStr">
         <is>
-          <t>635585.8093778668</t>
+          <t>635585.8093778649</t>
         </is>
       </c>
       <c r="BQ33" t="inlineStr">
@@ -17012,7 +17012,7 @@
       </c>
       <c r="CP33" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ33" t="inlineStr">
@@ -17052,12 +17052,12 @@
       </c>
       <c r="CX33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -17119,37 +17119,37 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-18 00:00:00</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-07 00:00:00</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -17159,12 +17159,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -17244,7 +17244,7 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-14 00:00:00</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
@@ -17341,12 +17341,12 @@
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>-91.80</t>
+          <t>-92.46</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
@@ -17356,7 +17356,7 @@
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>4713207.549800797</t>
+          <t>10786641.06200787</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr">
@@ -17382,12 +17382,12 @@
       </c>
       <c r="BO34" t="inlineStr">
         <is>
-          <t>531956.4574583338</t>
+          <t>531956.4574583224</t>
         </is>
       </c>
       <c r="BP34" t="inlineStr">
         <is>
-          <t>840514.7029655799</t>
+          <t>840514.7029655781</t>
         </is>
       </c>
       <c r="BQ34" t="inlineStr">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="CP34" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="CQ34" t="inlineStr">
@@ -17557,12 +17557,12 @@
       </c>
       <c r="CX34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="CY34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -17624,7 +17624,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -17749,7 +17749,7 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>2025-10-20 00:00:00</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
@@ -17843,12 +17843,12 @@
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>-124.93</t>
+          <t>-117.91</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
@@ -17858,7 +17858,7 @@
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>39232792.75697211</t>
+          <t>44220066.20669292</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr">
@@ -17884,12 +17884,12 @@
       </c>
       <c r="BO35" t="inlineStr">
         <is>
-          <t>-10828.63199754279</t>
+          <t>-10828.63199756098</t>
         </is>
       </c>
       <c r="BP35" t="inlineStr">
         <is>
-          <t>-618122.9880875144</t>
+          <t>-618122.98808752</t>
         </is>
       </c>
       <c r="BQ35" t="inlineStr">
@@ -18059,12 +18059,12 @@
       </c>
       <c r="CX35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="CY35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -18126,7 +18126,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -18251,7 +18251,7 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>2025-10-20 00:00:00</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
@@ -18345,12 +18345,12 @@
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>-123.77</t>
+          <t>-117.07</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>39232792.75697211</t>
+          <t>44220066.20669292</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr">
@@ -18386,12 +18386,12 @@
       </c>
       <c r="BO36" t="inlineStr">
         <is>
-          <t>99588.52365517932</t>
+          <t>99588.52365515885</t>
         </is>
       </c>
       <c r="BP36" t="inlineStr">
         <is>
-          <t>-303862.8232413512</t>
+          <t>-303862.8232413568</t>
         </is>
       </c>
       <c r="BQ36" t="inlineStr">
@@ -18561,12 +18561,12 @@
       </c>
       <c r="CX36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="CY36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -18628,7 +18628,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -18753,7 +18753,7 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>2025-10-20 00:00:00</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
@@ -18847,12 +18847,12 @@
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>-121.77</t>
+          <t>-115.64</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
@@ -18862,7 +18862,7 @@
       </c>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>39232792.75697211</t>
+          <t>44220066.20669292</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr">
@@ -18888,12 +18888,12 @@
       </c>
       <c r="BO37" t="inlineStr">
         <is>
-          <t>172943.314000003</t>
+          <t>172943.3139999799</t>
         </is>
       </c>
       <c r="BP37" t="inlineStr">
         <is>
-          <t>430514.4773689322</t>
+          <t>430514.4773689248</t>
         </is>
       </c>
       <c r="BQ37" t="inlineStr">
@@ -19063,12 +19063,12 @@
       </c>
       <c r="CX37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="CY37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -19130,7 +19130,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -19255,7 +19255,7 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>2025-10-20 00:00:00</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
@@ -19349,12 +19349,12 @@
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BG38" t="inlineStr">
         <is>
-          <t>-120.01</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="BH38" t="inlineStr">
@@ -19364,7 +19364,7 @@
       </c>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>39232792.75697211</t>
+          <t>44220066.20669292</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr">
@@ -19390,12 +19390,12 @@
       </c>
       <c r="BO38" t="inlineStr">
         <is>
-          <t>126112.1933874704</t>
+          <t>126112.1933874444</t>
         </is>
       </c>
       <c r="BP38" t="inlineStr">
         <is>
-          <t>552189.4969061613</t>
+          <t>552189.4969061539</t>
         </is>
       </c>
       <c r="BQ38" t="inlineStr">
@@ -19565,12 +19565,12 @@
       </c>
       <c r="CX38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="CY38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -19632,7 +19632,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -19757,7 +19757,7 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>2025-10-20 00:00:00</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
@@ -19851,12 +19851,12 @@
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BG39" t="inlineStr">
         <is>
-          <t>-119.51</t>
+          <t>-114.01</t>
         </is>
       </c>
       <c r="BH39" t="inlineStr">
@@ -19866,7 +19866,7 @@
       </c>
       <c r="BI39" t="inlineStr">
         <is>
-          <t>39232792.75697211</t>
+          <t>44220066.20669292</t>
         </is>
       </c>
       <c r="BJ39" t="inlineStr">
@@ -19892,12 +19892,12 @@
       </c>
       <c r="BO39" t="inlineStr">
         <is>
-          <t>48643.59274770846</t>
+          <t>48643.59274767908</t>
         </is>
       </c>
       <c r="BP39" t="inlineStr">
         <is>
-          <t>597595.0784984082</t>
+          <t>597595.0784984007</t>
         </is>
       </c>
       <c r="BQ39" t="inlineStr">
@@ -20067,12 +20067,12 @@
       </c>
       <c r="CX39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="CY39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -20134,7 +20134,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -20259,7 +20259,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>2025-10-20 00:00:00</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
@@ -20353,12 +20353,12 @@
       </c>
       <c r="BF40" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BG40" t="inlineStr">
         <is>
-          <t>-120.04</t>
+          <t>-114.39</t>
         </is>
       </c>
       <c r="BH40" t="inlineStr">
@@ -20368,7 +20368,7 @@
       </c>
       <c r="BI40" t="inlineStr">
         <is>
-          <t>39232792.75697211</t>
+          <t>44220066.20669292</t>
         </is>
       </c>
       <c r="BJ40" t="inlineStr">
@@ -20394,12 +20394,12 @@
       </c>
       <c r="BO40" t="inlineStr">
         <is>
-          <t>-51165.76829787332</t>
+          <t>-51165.76829790669</t>
         </is>
       </c>
       <c r="BP40" t="inlineStr">
         <is>
-          <t>551498.6208266765</t>
+          <t>551498.620826669</t>
         </is>
       </c>
       <c r="BQ40" t="inlineStr">
@@ -20569,12 +20569,12 @@
       </c>
       <c r="CX40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="CY40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -20636,7 +20636,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>2025-10-20 00:00:00</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
@@ -20855,12 +20855,12 @@
       </c>
       <c r="BF41" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BG41" t="inlineStr">
         <is>
-          <t>-120.47</t>
+          <t>-114.71</t>
         </is>
       </c>
       <c r="BH41" t="inlineStr">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="BI41" t="inlineStr">
         <is>
-          <t>39232792.75697211</t>
+          <t>44220066.20669292</t>
         </is>
       </c>
       <c r="BJ41" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="BO41" t="inlineStr">
         <is>
-          <t>-160741.1117750642</t>
+          <t>-160741.1117751023</t>
         </is>
       </c>
       <c r="BP41" t="inlineStr">
         <is>
-          <t>601141.4091232494</t>
+          <t>601141.4091232419</t>
         </is>
       </c>
       <c r="BQ41" t="inlineStr">
@@ -21071,12 +21071,12 @@
       </c>
       <c r="CX41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="CY41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -21263,7 +21263,7 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>2025-10-20 00:00:00</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
@@ -21357,12 +21357,12 @@
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BG42" t="inlineStr">
         <is>
-          <t>-121.02</t>
+          <t>-115.10</t>
         </is>
       </c>
       <c r="BH42" t="inlineStr">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="BI42" t="inlineStr">
         <is>
-          <t>39232792.75697211</t>
+          <t>44220066.20669292</t>
         </is>
       </c>
       <c r="BJ42" t="inlineStr">
@@ -21398,12 +21398,12 @@
       </c>
       <c r="BO42" t="inlineStr">
         <is>
-          <t>-299265.2064838485</t>
+          <t>-299265.2064838922</t>
         </is>
       </c>
       <c r="BP42" t="inlineStr">
         <is>
-          <t>-379860.3722074721</t>
+          <t>-379860.3722074796</t>
         </is>
       </c>
       <c r="BQ42" t="inlineStr">
@@ -21573,12 +21573,12 @@
       </c>
       <c r="CX42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CY42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -21640,7 +21640,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -21765,7 +21765,7 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>2025-10-20 00:00:00</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
@@ -21859,12 +21859,12 @@
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BG43" t="inlineStr">
         <is>
-          <t>-121.99</t>
+          <t>-115.80</t>
         </is>
       </c>
       <c r="BH43" t="inlineStr">
@@ -21874,7 +21874,7 @@
       </c>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>39232792.75697211</t>
+          <t>44220066.20669292</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="BO43" t="inlineStr">
         <is>
-          <t>-284611.5399886442</t>
+          <t>-284611.5399886945</t>
         </is>
       </c>
       <c r="BP43" t="inlineStr">
         <is>
-          <t>-769589.3679582383</t>
+          <t>-769589.3679582477</t>
         </is>
       </c>
       <c r="BQ43" t="inlineStr">
@@ -22075,12 +22075,12 @@
       </c>
       <c r="CX43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CY43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -22142,7 +22142,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -22267,7 +22267,7 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>2025-10-20 00:00:00</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
@@ -22361,12 +22361,12 @@
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BG44" t="inlineStr">
         <is>
-          <t>-122.31</t>
+          <t>-116.02</t>
         </is>
       </c>
       <c r="BH44" t="inlineStr">
@@ -22376,7 +22376,7 @@
       </c>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>39232792.75697211</t>
+          <t>44220066.20669292</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr">
@@ -22402,12 +22402,12 @@
       </c>
       <c r="BO44" t="inlineStr">
         <is>
-          <t>-196433.7530850817</t>
+          <t>-196433.7530851394</t>
         </is>
       </c>
       <c r="BP44" t="inlineStr">
         <is>
-          <t>-226223.4558893982</t>
+          <t>-226223.4558894094</t>
         </is>
       </c>
       <c r="BQ44" t="inlineStr">
@@ -22577,12 +22577,12 @@
       </c>
       <c r="CX44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="CY44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -22644,7 +22644,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -22769,7 +22769,7 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>2025-10-20 00:00:00</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
@@ -22863,12 +22863,12 @@
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-116.65</t>
         </is>
       </c>
       <c r="BH45" t="inlineStr">
@@ -22878,7 +22878,7 @@
       </c>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>39232792.75697211</t>
+          <t>44220066.20669292</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr">
@@ -22904,12 +22904,12 @@
       </c>
       <c r="BO45" t="inlineStr">
         <is>
-          <t>-191017.4434842968</t>
+          <t>-191017.443484363</t>
         </is>
       </c>
       <c r="BP45" t="inlineStr">
         <is>
-          <t>-95404.85093786009</t>
+          <t>-95404.85093787313</t>
         </is>
       </c>
       <c r="BQ45" t="inlineStr">
@@ -23079,12 +23079,12 @@
       </c>
       <c r="CX45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="CY45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -23146,7 +23146,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -23241,12 +23241,12 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/12</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
@@ -23367,12 +23367,12 @@
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr">
         <is>
-          <t>-70.78</t>
+          <t>-74.03</t>
         </is>
       </c>
       <c r="BH46" t="inlineStr">
@@ -23382,7 +23382,7 @@
       </c>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>9884931.66932271</t>
+          <t>10194200.81102362</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr">
@@ -23408,12 +23408,12 @@
       </c>
       <c r="BO46" t="inlineStr">
         <is>
-          <t>58777.12963741496</t>
+          <t>58777.1296374517</t>
         </is>
       </c>
       <c r="BP46" t="inlineStr">
         <is>
-          <t>45287.65797312465</t>
+          <t>45287.6579731321</t>
         </is>
       </c>
       <c r="BQ46" t="inlineStr">
@@ -23543,7 +23543,7 @@
       </c>
       <c r="CP46" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ46" t="inlineStr">
@@ -23583,12 +23583,12 @@
       </c>
       <c r="CX46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CY46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -23650,7 +23650,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -23745,12 +23745,12 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/12</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
@@ -23871,12 +23871,12 @@
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BG47" t="inlineStr">
         <is>
-          <t>-68.79</t>
+          <t>-72.26</t>
         </is>
       </c>
       <c r="BH47" t="inlineStr">
@@ -23886,7 +23886,7 @@
       </c>
       <c r="BI47" t="inlineStr">
         <is>
-          <t>9884931.66932271</t>
+          <t>10194200.81102362</t>
         </is>
       </c>
       <c r="BJ47" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="BO47" t="inlineStr">
         <is>
-          <t>61229.76084910411</t>
+          <t>61229.76084914617</t>
         </is>
       </c>
       <c r="BP47" t="inlineStr">
         <is>
-          <t>-21867.27685554512</t>
+          <t>-21867.27685553581</t>
         </is>
       </c>
       <c r="BQ47" t="inlineStr">
@@ -24047,7 +24047,7 @@
       </c>
       <c r="CP47" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ47" t="inlineStr">
@@ -24087,12 +24087,12 @@
       </c>
       <c r="CX47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CY47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -24154,7 +24154,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -24249,12 +24249,12 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/12</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
@@ -24375,12 +24375,12 @@
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BG48" t="inlineStr">
         <is>
-          <t>-67.02</t>
+          <t>-70.70</t>
         </is>
       </c>
       <c r="BH48" t="inlineStr">
@@ -24390,7 +24390,7 @@
       </c>
       <c r="BI48" t="inlineStr">
         <is>
-          <t>9884931.66932271</t>
+          <t>10194200.81102362</t>
         </is>
       </c>
       <c r="BJ48" t="inlineStr">
@@ -24416,12 +24416,12 @@
       </c>
       <c r="BO48" t="inlineStr">
         <is>
-          <t>76338.31315904034</t>
+          <t>76338.31315908834</t>
         </is>
       </c>
       <c r="BP48" t="inlineStr">
         <is>
-          <t>50633.1832769094</t>
+          <t>50633.18327691965</t>
         </is>
       </c>
       <c r="BQ48" t="inlineStr">
@@ -24551,7 +24551,7 @@
       </c>
       <c r="CP48" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ48" t="inlineStr">
@@ -24591,12 +24591,12 @@
       </c>
       <c r="CX48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CY48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -24658,7 +24658,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -24753,12 +24753,12 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/12</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
@@ -24879,12 +24879,12 @@
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr">
         <is>
-          <t>-67.66</t>
+          <t>-71.26</t>
         </is>
       </c>
       <c r="BH49" t="inlineStr">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>9884931.66932271</t>
+          <t>10194200.81102362</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr">
@@ -24920,12 +24920,12 @@
       </c>
       <c r="BO49" t="inlineStr">
         <is>
-          <t>81011.97313760959</t>
+          <t>81011.97313766446</t>
         </is>
       </c>
       <c r="BP49" t="inlineStr">
         <is>
-          <t>217255.7626348138</t>
+          <t>217255.7626348259</t>
         </is>
       </c>
       <c r="BQ49" t="inlineStr">
@@ -25055,7 +25055,7 @@
       </c>
       <c r="CP49" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ49" t="inlineStr">
@@ -25095,12 +25095,12 @@
       </c>
       <c r="CX49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CY49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -25162,7 +25162,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -25257,12 +25257,12 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/12</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
@@ -25383,12 +25383,12 @@
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr">
         <is>
-          <t>-69.96</t>
+          <t>-73.31</t>
         </is>
       </c>
       <c r="BH50" t="inlineStr">
@@ -25398,7 +25398,7 @@
       </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>9884931.66932271</t>
+          <t>10194200.81102362</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr">
@@ -25424,12 +25424,12 @@
       </c>
       <c r="BO50" t="inlineStr">
         <is>
-          <t>56240.37504720882</t>
+          <t>56240.37504727147</t>
         </is>
       </c>
       <c r="BP50" t="inlineStr">
         <is>
-          <t>264061.0987662897</t>
+          <t>264061.0987663036</t>
         </is>
       </c>
       <c r="BQ50" t="inlineStr">
@@ -25559,7 +25559,7 @@
       </c>
       <c r="CP50" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ50" t="inlineStr">
@@ -25599,12 +25599,12 @@
       </c>
       <c r="CX50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="CY50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -25666,7 +25666,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -25761,12 +25761,12 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/12</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
@@ -25887,12 +25887,12 @@
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BG51" t="inlineStr">
         <is>
-          <t>-72.59</t>
+          <t>-75.64</t>
         </is>
       </c>
       <c r="BH51" t="inlineStr">
@@ -25902,7 +25902,7 @@
       </c>
       <c r="BI51" t="inlineStr">
         <is>
-          <t>9884931.66932271</t>
+          <t>10194200.81102362</t>
         </is>
       </c>
       <c r="BJ51" t="inlineStr">
@@ -25928,12 +25928,12 @@
       </c>
       <c r="BO51" t="inlineStr">
         <is>
-          <t>18454.78891646684</t>
+          <t>18454.78891653835</t>
         </is>
       </c>
       <c r="BP51" t="inlineStr">
         <is>
-          <t>307941.0039981743</t>
+          <t>307941.0039981902</t>
         </is>
       </c>
       <c r="BQ51" t="inlineStr">
@@ -26063,7 +26063,7 @@
       </c>
       <c r="CP51" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ51" t="inlineStr">
@@ -26103,12 +26103,12 @@
       </c>
       <c r="CX51" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="CY51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -26170,7 +26170,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -26265,12 +26265,12 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/12</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
@@ -26391,12 +26391,12 @@
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BG52" t="inlineStr">
         <is>
-          <t>-74.74</t>
+          <t>-77.56</t>
         </is>
       </c>
       <c r="BH52" t="inlineStr">
@@ -26406,7 +26406,7 @@
       </c>
       <c r="BI52" t="inlineStr">
         <is>
-          <t>9884931.66932271</t>
+          <t>10194200.81102362</t>
         </is>
       </c>
       <c r="BJ52" t="inlineStr">
@@ -26432,12 +26432,12 @@
       </c>
       <c r="BO52" t="inlineStr">
         <is>
-          <t>-34179.06837111634</t>
+          <t>-34179.06837103471</t>
         </is>
       </c>
       <c r="BP52" t="inlineStr">
         <is>
-          <t>125241.2613295028</t>
+          <t>125241.2613295205</t>
         </is>
       </c>
       <c r="BQ52" t="inlineStr">
@@ -26567,7 +26567,7 @@
       </c>
       <c r="CP52" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ52" t="inlineStr">
@@ -26607,12 +26607,12 @@
       </c>
       <c r="CX52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="CY52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -26674,7 +26674,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -26769,12 +26769,12 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/12</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
@@ -26895,12 +26895,12 @@
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BG53" t="inlineStr">
         <is>
-          <t>-75.20</t>
+          <t>-77.96</t>
         </is>
       </c>
       <c r="BH53" t="inlineStr">
@@ -26910,7 +26910,7 @@
       </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>9884931.66932271</t>
+          <t>10194200.81102362</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr">
@@ -26936,12 +26936,12 @@
       </c>
       <c r="BO53" t="inlineStr">
         <is>
-          <t>-63164.582862138</t>
+          <t>-63164.58286204475</t>
         </is>
       </c>
       <c r="BP53" t="inlineStr">
         <is>
-          <t>-213357.0232446529</t>
+          <t>-213357.0232446333</t>
         </is>
       </c>
       <c r="BQ53" t="inlineStr">
@@ -27071,7 +27071,7 @@
       </c>
       <c r="CP53" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ53" t="inlineStr">
@@ -27111,12 +27111,12 @@
       </c>
       <c r="CX53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="CY53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -27178,7 +27178,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -27273,12 +27273,12 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/12</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr">
@@ -27399,12 +27399,12 @@
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BG54" t="inlineStr">
         <is>
-          <t>-74.82</t>
+          <t>-77.62</t>
         </is>
       </c>
       <c r="BH54" t="inlineStr">
@@ -27414,7 +27414,7 @@
       </c>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>9884931.66932271</t>
+          <t>10194200.81102362</t>
         </is>
       </c>
       <c r="BJ54" t="inlineStr">
@@ -27440,12 +27440,12 @@
       </c>
       <c r="BO54" t="inlineStr">
         <is>
-          <t>-35856.86642895347</t>
+          <t>-35856.86642884682</t>
         </is>
       </c>
       <c r="BP54" t="inlineStr">
         <is>
-          <t>-212814.7503775661</t>
+          <t>-212814.7503775437</t>
         </is>
       </c>
       <c r="BQ54" t="inlineStr">
@@ -27575,7 +27575,7 @@
       </c>
       <c r="CP54" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ54" t="inlineStr">
@@ -27615,12 +27615,12 @@
       </c>
       <c r="CX54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="CY54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -27682,7 +27682,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -27777,12 +27777,12 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/12</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
@@ -27903,12 +27903,12 @@
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BG55" t="inlineStr">
         <is>
-          <t>-74.38</t>
+          <t>-77.24</t>
         </is>
       </c>
       <c r="BH55" t="inlineStr">
@@ -27918,7 +27918,7 @@
       </c>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>9884931.66932271</t>
+          <t>10194200.81102362</t>
         </is>
       </c>
       <c r="BJ55" t="inlineStr">
@@ -27944,12 +27944,12 @@
       </c>
       <c r="BO55" t="inlineStr">
         <is>
-          <t>-3682.705711023906</t>
+          <t>-3682.705710901928</t>
         </is>
       </c>
       <c r="BP55" t="inlineStr">
         <is>
-          <t>-41278.11948252935</t>
+          <t>-41278.11948250327</t>
         </is>
       </c>
       <c r="BQ55" t="inlineStr">
@@ -28079,7 +28079,7 @@
       </c>
       <c r="CP55" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ55" t="inlineStr">
@@ -28119,12 +28119,12 @@
       </c>
       <c r="CX55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="CY55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -28186,7 +28186,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -28281,12 +28281,12 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/12</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
@@ -28407,12 +28407,12 @@
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BG56" t="inlineStr">
         <is>
-          <t>-74.47</t>
+          <t>-77.31</t>
         </is>
       </c>
       <c r="BH56" t="inlineStr">
@@ -28422,7 +28422,7 @@
       </c>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>9884931.66932271</t>
+          <t>10194200.81102362</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr">
@@ -28448,12 +28448,12 @@
       </c>
       <c r="BO56" t="inlineStr">
         <is>
-          <t>3152.824065613448</t>
+          <t>3152.824065752862</t>
         </is>
       </c>
       <c r="BP56" t="inlineStr">
         <is>
-          <t>-146526.1067938153</t>
+          <t>-146526.1067937855</t>
         </is>
       </c>
       <c r="BQ56" t="inlineStr">
@@ -28583,7 +28583,7 @@
       </c>
       <c r="CP56" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ56" t="inlineStr">
@@ -28623,12 +28623,12 @@
       </c>
       <c r="CX56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="CY56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -28690,37 +28690,37 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-05 00:00:00</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-14 00:00:00</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -28730,12 +28730,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -28745,12 +28745,12 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-8.50</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-13.14</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -28815,7 +28815,7 @@
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
@@ -28910,12 +28910,12 @@
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BG57" t="inlineStr">
         <is>
-          <t>-143.91</t>
+          <t>-144.57</t>
         </is>
       </c>
       <c r="BH57" t="inlineStr">
@@ -28925,7 +28925,7 @@
       </c>
       <c r="BI57" t="inlineStr">
         <is>
-          <t>509236690.2908367</t>
+          <t>500627389.9053254</t>
         </is>
       </c>
       <c r="BJ57" t="inlineStr">
@@ -28951,7 +28951,7 @@
       </c>
       <c r="BO57" t="inlineStr">
         <is>
-          <t>-18210111.15752108</t>
+          <t>-18210111.15752111</t>
         </is>
       </c>
       <c r="BP57" t="inlineStr">
@@ -29126,12 +29126,12 @@
       </c>
       <c r="CX57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="CY57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -29193,37 +29193,37 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-05 00:00:00</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-14 00:00:00</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -29233,12 +29233,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -29248,12 +29248,12 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-10.07</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-13.14</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
@@ -29413,12 +29413,12 @@
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BG58" t="inlineStr">
         <is>
-          <t>-141.27</t>
+          <t>-141.90</t>
         </is>
       </c>
       <c r="BH58" t="inlineStr">
@@ -29428,7 +29428,7 @@
       </c>
       <c r="BI58" t="inlineStr">
         <is>
-          <t>509236690.2908367</t>
+          <t>500627389.9053254</t>
         </is>
       </c>
       <c r="BJ58" t="inlineStr">
@@ -29454,7 +29454,7 @@
       </c>
       <c r="BO58" t="inlineStr">
         <is>
-          <t>-17090269.70521886</t>
+          <t>-17090269.7052189</t>
         </is>
       </c>
       <c r="BP58" t="inlineStr">
@@ -29629,12 +29629,12 @@
       </c>
       <c r="CX58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="CY58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -29696,37 +29696,37 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-05 00:00:00</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-14 00:00:00</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -29736,12 +29736,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -29751,12 +29751,12 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.54</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-13.14</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -29821,7 +29821,7 @@
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL59" t="inlineStr">
@@ -29916,12 +29916,12 @@
       </c>
       <c r="BF59" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BG59" t="inlineStr">
         <is>
-          <t>-137.76</t>
+          <t>-138.34</t>
         </is>
       </c>
       <c r="BH59" t="inlineStr">
@@ -29931,7 +29931,7 @@
       </c>
       <c r="BI59" t="inlineStr">
         <is>
-          <t>509236690.2908367</t>
+          <t>500627389.9053254</t>
         </is>
       </c>
       <c r="BJ59" t="inlineStr">
@@ -29957,7 +29957,7 @@
       </c>
       <c r="BO59" t="inlineStr">
         <is>
-          <t>-16225303.72444985</t>
+          <t>-16225303.72444989</t>
         </is>
       </c>
       <c r="BP59" t="inlineStr">
@@ -30132,12 +30132,12 @@
       </c>
       <c r="CX59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="CY59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -30199,37 +30199,37 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-05 00:00:00</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-14 00:00:00</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -30239,12 +30239,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -30254,12 +30254,12 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-13.14</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL60" t="inlineStr">
@@ -30419,12 +30419,12 @@
       </c>
       <c r="BF60" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BG60" t="inlineStr">
         <is>
-          <t>-134.67</t>
+          <t>-135.19</t>
         </is>
       </c>
       <c r="BH60" t="inlineStr">
@@ -30434,7 +30434,7 @@
       </c>
       <c r="BI60" t="inlineStr">
         <is>
-          <t>509236690.2908367</t>
+          <t>500627389.9053254</t>
         </is>
       </c>
       <c r="BJ60" t="inlineStr">
@@ -30460,7 +30460,7 @@
       </c>
       <c r="BO60" t="inlineStr">
         <is>
-          <t>-16352234.65905295</t>
+          <t>-16352234.65905299</t>
         </is>
       </c>
       <c r="BP60" t="inlineStr">
@@ -30635,12 +30635,12 @@
       </c>
       <c r="CX60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="CY60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -30702,37 +30702,37 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-05 00:00:00</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-14 00:00:00</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -30742,12 +30742,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -30757,12 +30757,12 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-13.14</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -30827,7 +30827,7 @@
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL61" t="inlineStr">
@@ -30922,12 +30922,12 @@
       </c>
       <c r="BF61" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BG61" t="inlineStr">
         <is>
-          <t>-132.17</t>
+          <t>-132.66</t>
         </is>
       </c>
       <c r="BH61" t="inlineStr">
@@ -30937,7 +30937,7 @@
       </c>
       <c r="BI61" t="inlineStr">
         <is>
-          <t>509236690.2908367</t>
+          <t>500627389.9053254</t>
         </is>
       </c>
       <c r="BJ61" t="inlineStr">
@@ -30963,7 +30963,7 @@
       </c>
       <c r="BO61" t="inlineStr">
         <is>
-          <t>-15790194.11551091</t>
+          <t>-15790194.11551096</t>
         </is>
       </c>
       <c r="BP61" t="inlineStr">
@@ -31138,12 +31138,12 @@
       </c>
       <c r="CX61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="CY61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -31205,37 +31205,37 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-05 00:00:00</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-14 00:00:00</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -31245,12 +31245,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -31260,12 +31260,12 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7.19</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-13.14</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -31330,7 +31330,7 @@
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
@@ -31425,12 +31425,12 @@
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BG62" t="inlineStr">
         <is>
-          <t>-129.71</t>
+          <t>-130.16</t>
         </is>
       </c>
       <c r="BH62" t="inlineStr">
@@ -31440,7 +31440,7 @@
       </c>
       <c r="BI62" t="inlineStr">
         <is>
-          <t>509236690.2908367</t>
+          <t>500627389.9053254</t>
         </is>
       </c>
       <c r="BJ62" t="inlineStr">
@@ -31466,7 +31466,7 @@
       </c>
       <c r="BO62" t="inlineStr">
         <is>
-          <t>-16094886.85023706</t>
+          <t>-16094886.85023712</t>
         </is>
       </c>
       <c r="BP62" t="inlineStr">
@@ -31641,12 +31641,12 @@
       </c>
       <c r="CX62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="CY62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -31708,37 +31708,37 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-05 00:00:00</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-14 00:00:00</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -31748,12 +31748,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -31763,12 +31763,12 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-13.14</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -31833,7 +31833,7 @@
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL63" t="inlineStr">
@@ -31928,12 +31928,12 @@
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BG63" t="inlineStr">
         <is>
-          <t>-127.08</t>
+          <t>-127.50</t>
         </is>
       </c>
       <c r="BH63" t="inlineStr">
@@ -31943,7 +31943,7 @@
       </c>
       <c r="BI63" t="inlineStr">
         <is>
-          <t>509236690.2908367</t>
+          <t>500627389.9053254</t>
         </is>
       </c>
       <c r="BJ63" t="inlineStr">
@@ -31969,7 +31969,7 @@
       </c>
       <c r="BO63" t="inlineStr">
         <is>
-          <t>-16653599.5564407</t>
+          <t>-16653599.55644078</t>
         </is>
       </c>
       <c r="BP63" t="inlineStr">
@@ -32144,12 +32144,12 @@
       </c>
       <c r="CX63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CY63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -32211,37 +32211,37 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-05 00:00:00</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-14 00:00:00</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -32251,12 +32251,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -32266,12 +32266,12 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-13.14</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -32336,7 +32336,7 @@
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
@@ -32431,12 +32431,12 @@
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BG64" t="inlineStr">
         <is>
-          <t>-124.28</t>
+          <t>-124.65</t>
         </is>
       </c>
       <c r="BH64" t="inlineStr">
@@ -32446,7 +32446,7 @@
       </c>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>509236690.2908367</t>
+          <t>500627389.9053254</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr">
@@ -32472,7 +32472,7 @@
       </c>
       <c r="BO64" t="inlineStr">
         <is>
-          <t>-18650994.25014966</t>
+          <t>-18650994.25014975</t>
         </is>
       </c>
       <c r="BP64" t="inlineStr">
@@ -32647,12 +32647,12 @@
       </c>
       <c r="CX64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="CY64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -32714,37 +32714,37 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-05 00:00:00</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-14 00:00:00</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -32754,12 +32754,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -32769,12 +32769,12 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7.71</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-13.14</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -32839,7 +32839,7 @@
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
@@ -32934,12 +32934,12 @@
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BG65" t="inlineStr">
         <is>
-          <t>-121.30</t>
+          <t>-121.62</t>
         </is>
       </c>
       <c r="BH65" t="inlineStr">
@@ -32949,7 +32949,7 @@
       </c>
       <c r="BI65" t="inlineStr">
         <is>
-          <t>509236690.2908367</t>
+          <t>500627389.9053254</t>
         </is>
       </c>
       <c r="BJ65" t="inlineStr">
@@ -32975,7 +32975,7 @@
       </c>
       <c r="BO65" t="inlineStr">
         <is>
-          <t>-20144984.69819575</t>
+          <t>-20144984.69819585</t>
         </is>
       </c>
       <c r="BP65" t="inlineStr">
@@ -33150,12 +33150,12 @@
       </c>
       <c r="CX65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="CY65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -33217,37 +33217,37 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-05 00:00:00</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-14 00:00:00</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -33257,12 +33257,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -33272,12 +33272,12 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7.19</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-13.14</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -33342,7 +33342,7 @@
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL66" t="inlineStr">
@@ -33437,12 +33437,12 @@
       </c>
       <c r="BF66" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BG66" t="inlineStr">
         <is>
-          <t>-117.24</t>
+          <t>-117.50</t>
         </is>
       </c>
       <c r="BH66" t="inlineStr">
@@ -33452,7 +33452,7 @@
       </c>
       <c r="BI66" t="inlineStr">
         <is>
-          <t>509236690.2908367</t>
+          <t>500627389.9053254</t>
         </is>
       </c>
       <c r="BJ66" t="inlineStr">
@@ -33478,7 +33478,7 @@
       </c>
       <c r="BO66" t="inlineStr">
         <is>
-          <t>-21578713.8120665</t>
+          <t>-21578713.81206662</t>
         </is>
       </c>
       <c r="BP66" t="inlineStr">
@@ -33653,12 +33653,12 @@
       </c>
       <c r="CX66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="CY66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -33720,37 +33720,37 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-05 00:00:00</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-14 00:00:00</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -33760,12 +33760,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -33775,12 +33775,12 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-13.14</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -33845,7 +33845,7 @@
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="AL67" t="inlineStr">
@@ -33940,12 +33940,12 @@
       </c>
       <c r="BF67" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BG67" t="inlineStr">
         <is>
-          <t>-113.70</t>
+          <t>-113.91</t>
         </is>
       </c>
       <c r="BH67" t="inlineStr">
@@ -33955,7 +33955,7 @@
       </c>
       <c r="BI67" t="inlineStr">
         <is>
-          <t>509236690.2908367</t>
+          <t>500627389.9053254</t>
         </is>
       </c>
       <c r="BJ67" t="inlineStr">
@@ -33981,7 +33981,7 @@
       </c>
       <c r="BO67" t="inlineStr">
         <is>
-          <t>-21831870.73320912</t>
+          <t>-21831870.73320927</t>
         </is>
       </c>
       <c r="BP67" t="inlineStr">
@@ -34156,12 +34156,12 @@
       </c>
       <c r="CX67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="CY67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -34223,37 +34223,37 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -34263,12 +34263,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -34278,12 +34278,12 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
@@ -34318,12 +34318,12 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG68" t="inlineStr">
@@ -34348,7 +34348,7 @@
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL68" t="inlineStr">
@@ -34460,7 +34460,7 @@
       </c>
       <c r="BI68" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ68" t="inlineStr">
@@ -34486,12 +34486,12 @@
       </c>
       <c r="BO68" t="inlineStr">
         <is>
-          <t>30618840.01772104</t>
+          <t>30618840.01772266</t>
         </is>
       </c>
       <c r="BP68" t="inlineStr">
         <is>
-          <t>-68640250.35247445</t>
+          <t>-68640250.3524741</t>
         </is>
       </c>
       <c r="BQ68" t="inlineStr">
@@ -34621,7 +34621,7 @@
       </c>
       <c r="CP68" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ68" t="inlineStr">
@@ -34661,12 +34661,12 @@
       </c>
       <c r="CX68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -34728,37 +34728,37 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -34768,12 +34768,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -34783,12 +34783,12 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -34823,12 +34823,12 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG69" t="inlineStr">
@@ -34853,7 +34853,7 @@
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
@@ -34965,7 +34965,7 @@
       </c>
       <c r="BI69" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ69" t="inlineStr">
@@ -34991,12 +34991,12 @@
       </c>
       <c r="BO69" t="inlineStr">
         <is>
-          <t>48665947.35775659</t>
+          <t>48665947.35775843</t>
         </is>
       </c>
       <c r="BP69" t="inlineStr">
         <is>
-          <t>-23798193.28764105</t>
+          <t>-23798193.28764057</t>
         </is>
       </c>
       <c r="BQ69" t="inlineStr">
@@ -35126,7 +35126,7 @@
       </c>
       <c r="CP69" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ69" t="inlineStr">
@@ -35166,12 +35166,12 @@
       </c>
       <c r="CX69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -35228,72 +35228,72 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -35328,12 +35328,12 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG70" t="inlineStr">
@@ -35358,7 +35358,7 @@
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
@@ -35470,7 +35470,7 @@
       </c>
       <c r="BI70" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ70" t="inlineStr">
@@ -35496,12 +35496,12 @@
       </c>
       <c r="BO70" t="inlineStr">
         <is>
-          <t>61841245.65691981</t>
+          <t>61841245.65692189</t>
         </is>
       </c>
       <c r="BP70" t="inlineStr">
         <is>
-          <t>1771378.3509655</t>
+          <t>1771378.350965977</t>
         </is>
       </c>
       <c r="BQ70" t="inlineStr">
@@ -35511,7 +35511,7 @@
       </c>
       <c r="BR70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="BS70" t="inlineStr">
@@ -35631,7 +35631,7 @@
       </c>
       <c r="CP70" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ70" t="inlineStr">
@@ -35671,12 +35671,12 @@
       </c>
       <c r="CX70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -35733,72 +35733,72 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -35833,12 +35833,12 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG71" t="inlineStr">
@@ -35863,7 +35863,7 @@
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL71" t="inlineStr">
@@ -35975,7 +35975,7 @@
       </c>
       <c r="BI71" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ71" t="inlineStr">
@@ -36001,12 +36001,12 @@
       </c>
       <c r="BO71" t="inlineStr">
         <is>
-          <t>72763039.71254787</t>
+          <t>72763039.71255024</t>
         </is>
       </c>
       <c r="BP71" t="inlineStr">
         <is>
-          <t>-3554777.034988403</t>
+          <t>-3554777.034987926</t>
         </is>
       </c>
       <c r="BQ71" t="inlineStr">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="BR71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="BS71" t="inlineStr">
@@ -36136,7 +36136,7 @@
       </c>
       <c r="CP71" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ71" t="inlineStr">
@@ -36176,12 +36176,12 @@
       </c>
       <c r="CX71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -36238,72 +36238,72 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.23</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
@@ -36338,12 +36338,12 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG72" t="inlineStr">
@@ -36368,7 +36368,7 @@
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
@@ -36480,7 +36480,7 @@
       </c>
       <c r="BI72" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ72" t="inlineStr">
@@ -36506,12 +36506,12 @@
       </c>
       <c r="BO72" t="inlineStr">
         <is>
-          <t>86639006.39391811</t>
+          <t>86639006.39392082</t>
         </is>
       </c>
       <c r="BP72" t="inlineStr">
         <is>
-          <t>5832399.164898872</t>
+          <t>5832399.164899349</t>
         </is>
       </c>
       <c r="BQ72" t="inlineStr">
@@ -36521,7 +36521,7 @@
       </c>
       <c r="BR72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="BS72" t="inlineStr">
@@ -36641,7 +36641,7 @@
       </c>
       <c r="CP72" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ72" t="inlineStr">
@@ -36681,12 +36681,12 @@
       </c>
       <c r="CX72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -36743,72 +36743,72 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.57</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
@@ -36843,12 +36843,12 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG73" t="inlineStr">
@@ -36873,7 +36873,7 @@
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL73" t="inlineStr">
@@ -36985,7 +36985,7 @@
       </c>
       <c r="BI73" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ73" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="BO73" t="inlineStr">
         <is>
-          <t>101331116.7991943</t>
+          <t>101331116.7991975</t>
         </is>
       </c>
       <c r="BP73" t="inlineStr">
         <is>
-          <t>17182923.94456267</t>
+          <t>17182923.94456339</t>
         </is>
       </c>
       <c r="BQ73" t="inlineStr">
@@ -37026,7 +37026,7 @@
       </c>
       <c r="BR73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="BS73" t="inlineStr">
@@ -37146,7 +37146,7 @@
       </c>
       <c r="CP73" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ73" t="inlineStr">
@@ -37186,12 +37186,12 @@
       </c>
       <c r="CX73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY73" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -37248,72 +37248,72 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
@@ -37348,12 +37348,12 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG74" t="inlineStr">
@@ -37378,7 +37378,7 @@
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL74" t="inlineStr">
@@ -37490,7 +37490,7 @@
       </c>
       <c r="BI74" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ74" t="inlineStr">
@@ -37516,12 +37516,12 @@
       </c>
       <c r="BO74" t="inlineStr">
         <is>
-          <t>116630788.2273092</t>
+          <t>116630788.2273128</t>
         </is>
       </c>
       <c r="BP74" t="inlineStr">
         <is>
-          <t>57971406.52463365</t>
+          <t>57971406.5246346</t>
         </is>
       </c>
       <c r="BQ74" t="inlineStr">
@@ -37531,7 +37531,7 @@
       </c>
       <c r="BR74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="BS74" t="inlineStr">
@@ -37651,7 +37651,7 @@
       </c>
       <c r="CP74" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ74" t="inlineStr">
@@ -37691,12 +37691,12 @@
       </c>
       <c r="CX74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CY74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -37753,72 +37753,72 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
@@ -37853,12 +37853,12 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG75" t="inlineStr">
@@ -37883,7 +37883,7 @@
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
@@ -37995,7 +37995,7 @@
       </c>
       <c r="BI75" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ75" t="inlineStr">
@@ -38021,12 +38021,12 @@
       </c>
       <c r="BO75" t="inlineStr">
         <is>
-          <t>127296130.3550684</t>
+          <t>127296130.3550724</t>
         </is>
       </c>
       <c r="BP75" t="inlineStr">
         <is>
-          <t>94147340.0488553</t>
+          <t>94147340.04885626</t>
         </is>
       </c>
       <c r="BQ75" t="inlineStr">
@@ -38036,7 +38036,7 @@
       </c>
       <c r="BR75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="BS75" t="inlineStr">
@@ -38156,7 +38156,7 @@
       </c>
       <c r="CP75" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ75" t="inlineStr">
@@ -38196,12 +38196,12 @@
       </c>
       <c r="CX75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -38258,72 +38258,72 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.72</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -38358,12 +38358,12 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG76" t="inlineStr">
@@ -38388,7 +38388,7 @@
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL76" t="inlineStr">
@@ -38500,7 +38500,7 @@
       </c>
       <c r="BI76" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ76" t="inlineStr">
@@ -38526,12 +38526,12 @@
       </c>
       <c r="BO76" t="inlineStr">
         <is>
-          <t>133323183.1380162</t>
+          <t>133323183.1380208</t>
         </is>
       </c>
       <c r="BP76" t="inlineStr">
         <is>
-          <t>133094332.7959986</t>
+          <t>133094332.7959998</t>
         </is>
       </c>
       <c r="BQ76" t="inlineStr">
@@ -38541,7 +38541,7 @@
       </c>
       <c r="BR76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="BS76" t="inlineStr">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="CP76" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ76" t="inlineStr">
@@ -38701,12 +38701,12 @@
       </c>
       <c r="CX76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -38763,72 +38763,72 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.72</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -38863,12 +38863,12 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG77" t="inlineStr">
@@ -38893,7 +38893,7 @@
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
@@ -39005,7 +39005,7 @@
       </c>
       <c r="BI77" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ77" t="inlineStr">
@@ -39031,12 +39031,12 @@
       </c>
       <c r="BO77" t="inlineStr">
         <is>
-          <t>133364792.2911103</t>
+          <t>133364792.2911156</t>
         </is>
       </c>
       <c r="BP77" t="inlineStr">
         <is>
-          <t>203187442.9063461</t>
+          <t>203187442.9063473</t>
         </is>
       </c>
       <c r="BQ77" t="inlineStr">
@@ -39046,7 +39046,7 @@
       </c>
       <c r="BR77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="BS77" t="inlineStr">
@@ -39166,7 +39166,7 @@
       </c>
       <c r="CP77" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ77" t="inlineStr">
@@ -39206,12 +39206,12 @@
       </c>
       <c r="CX77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -39268,72 +39268,72 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
@@ -39368,12 +39368,12 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AG78" t="inlineStr">
@@ -39398,7 +39398,7 @@
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
@@ -39510,7 +39510,7 @@
       </c>
       <c r="BI78" t="inlineStr">
         <is>
-          <t>1126349490.825301</t>
+          <t>933915779.7094862</t>
         </is>
       </c>
       <c r="BJ78" t="inlineStr">
@@ -39536,12 +39536,12 @@
       </c>
       <c r="BO78" t="inlineStr">
         <is>
-          <t>120669764.906522</t>
+          <t>120669764.906528</t>
         </is>
       </c>
       <c r="BP78" t="inlineStr">
         <is>
-          <t>150759058.674473</t>
+          <t>150759058.6744742</t>
         </is>
       </c>
       <c r="BQ78" t="inlineStr">
@@ -39551,7 +39551,7 @@
       </c>
       <c r="BR78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="BS78" t="inlineStr">
@@ -39671,7 +39671,7 @@
       </c>
       <c r="CP78" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CQ78" t="inlineStr">
@@ -39711,12 +39711,12 @@
       </c>
       <c r="CX78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CY78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
